--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L657"/>
+  <dimension ref="A1:L660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28024,6 +28024,132 @@
         <v>345.12</v>
       </c>
       <c r="L657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="C658" t="n">
+        <v>372</v>
+      </c>
+      <c r="D658" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="E658" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="F658" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="G658" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="H658" t="n">
+        <v>377.04</v>
+      </c>
+      <c r="I658" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="J658" t="n">
+        <v>342.93</v>
+      </c>
+      <c r="K658" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:08+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>395.15</v>
+      </c>
+      <c r="C659" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="D659" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="E659" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="F659" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="G659" t="n">
+        <v>370.64</v>
+      </c>
+      <c r="H659" t="n">
+        <v>375.87</v>
+      </c>
+      <c r="I659" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="J659" t="n">
+        <v>343.27</v>
+      </c>
+      <c r="K659" t="n">
+        <v>348.13</v>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>393.62</v>
+      </c>
+      <c r="C660" t="n">
+        <v>369.57</v>
+      </c>
+      <c r="D660" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="E660" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="F660" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="G660" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="H660" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="I660" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="J660" t="n">
+        <v>344.84</v>
+      </c>
+      <c r="K660" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="L660" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28040,7 +28166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34853,6 +34979,36 @@
       </c>
       <c r="B681" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -35021,28 +35177,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5944999218906309</v>
+        <v>0.5779242330297774</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04074865317602838</v>
+        <v>0.03882547091760158</v>
       </c>
       <c r="M2" t="n">
-        <v>15.07112050414455</v>
+        <v>15.04046904987942</v>
       </c>
       <c r="N2" t="n">
-        <v>458.6651306552735</v>
+        <v>458.1509577005945</v>
       </c>
       <c r="O2" t="n">
-        <v>21.41646867845569</v>
+        <v>21.40446116351903</v>
       </c>
       <c r="P2" t="n">
-        <v>397.028919906426</v>
+        <v>397.201028602694</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35099,28 +35255,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04868458827080049</v>
+        <v>0.04821849546078461</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K3" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01123905048999918</v>
+        <v>0.01112738946215952</v>
       </c>
       <c r="M3" t="n">
-        <v>2.630415824554514</v>
+        <v>2.623139053770883</v>
       </c>
       <c r="N3" t="n">
-        <v>11.49522957254929</v>
+        <v>11.44868578867984</v>
       </c>
       <c r="O3" t="n">
-        <v>3.390461557450444</v>
+        <v>3.383590665059803</v>
       </c>
       <c r="P3" t="n">
-        <v>369.9654437883419</v>
+        <v>369.970290380936</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35177,28 +35333,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1908940879358607</v>
+        <v>-0.1930865830460683</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K4" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1273712188212801</v>
+        <v>0.1307543710951681</v>
       </c>
       <c r="M4" t="n">
-        <v>2.847825615783222</v>
+        <v>2.846586623843867</v>
       </c>
       <c r="N4" t="n">
-        <v>13.76309625727159</v>
+        <v>13.73320048267128</v>
       </c>
       <c r="O4" t="n">
-        <v>3.709864722233359</v>
+        <v>3.705833304760386</v>
       </c>
       <c r="P4" t="n">
-        <v>367.5621501733735</v>
+        <v>367.584922699655</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35255,28 +35411,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1449203005243445</v>
+        <v>-0.1464124092747065</v>
       </c>
       <c r="J5" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K5" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09166478660314781</v>
+        <v>0.09407370386287195</v>
       </c>
       <c r="M5" t="n">
-        <v>2.591180255184846</v>
+        <v>2.586995101698226</v>
       </c>
       <c r="N5" t="n">
-        <v>11.50527716622775</v>
+        <v>11.47027209906662</v>
       </c>
       <c r="O5" t="n">
-        <v>3.391942978033056</v>
+        <v>3.38677901538713</v>
       </c>
       <c r="P5" t="n">
-        <v>368.3762225300936</v>
+        <v>368.3917059691648</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35333,28 +35489,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1936629188017295</v>
+        <v>-0.1979807226152018</v>
       </c>
       <c r="J6" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K6" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1655513934485915</v>
+        <v>0.1715635115062797</v>
       </c>
       <c r="M6" t="n">
-        <v>2.520961383335943</v>
+        <v>2.53241469969514</v>
       </c>
       <c r="N6" t="n">
-        <v>10.43618146105051</v>
+        <v>10.50183804215711</v>
       </c>
       <c r="O6" t="n">
-        <v>3.230507926170513</v>
+        <v>3.240653952855366</v>
       </c>
       <c r="P6" t="n">
-        <v>381.7676946773427</v>
+        <v>381.8125124265875</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35411,28 +35567,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03652956346654661</v>
+        <v>-0.03812637608808075</v>
       </c>
       <c r="J7" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K7" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007063691808671169</v>
+        <v>0.007752024421546988</v>
       </c>
       <c r="M7" t="n">
-        <v>2.337899083272859</v>
+        <v>2.336150187585824</v>
       </c>
       <c r="N7" t="n">
-        <v>10.35524876193211</v>
+        <v>10.32384220993114</v>
       </c>
       <c r="O7" t="n">
-        <v>3.217957234323059</v>
+        <v>3.213073639045818</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5383506431771</v>
+        <v>373.5549256826286</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35489,28 +35645,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1978497981326842</v>
+        <v>-0.2010310869931074</v>
       </c>
       <c r="J8" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K8" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1294070419654071</v>
+        <v>0.133689175670525</v>
       </c>
       <c r="M8" t="n">
-        <v>2.803380787858278</v>
+        <v>2.805676277445377</v>
       </c>
       <c r="N8" t="n">
-        <v>14.44360179450774</v>
+        <v>14.43662850642227</v>
       </c>
       <c r="O8" t="n">
-        <v>3.800473890780956</v>
+        <v>3.799556356526677</v>
       </c>
       <c r="P8" t="n">
-        <v>385.0116424950274</v>
+        <v>385.0448009397102</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35567,28 +35723,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.287236907225272</v>
+        <v>-0.2950241905388595</v>
       </c>
       <c r="J9" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K9" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1434711369644858</v>
+        <v>0.1497794055719412</v>
       </c>
       <c r="M9" t="n">
-        <v>4.044777256145174</v>
+        <v>4.060036251722478</v>
       </c>
       <c r="N9" t="n">
-        <v>27.0150011117743</v>
+        <v>27.23683353124331</v>
       </c>
       <c r="O9" t="n">
-        <v>5.197595704917255</v>
+        <v>5.218891983097879</v>
       </c>
       <c r="P9" t="n">
-        <v>368.578299176997</v>
+        <v>368.6594571208331</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35645,28 +35801,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4906498938927737</v>
+        <v>-0.4984854037691365</v>
       </c>
       <c r="J10" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K10" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1879708735796519</v>
+        <v>0.193400026388085</v>
       </c>
       <c r="M10" t="n">
-        <v>6.347298138811153</v>
+        <v>6.356371096363273</v>
       </c>
       <c r="N10" t="n">
-        <v>57.03894833176471</v>
+        <v>57.13055073036779</v>
       </c>
       <c r="O10" t="n">
-        <v>7.552413411073623</v>
+        <v>7.558475423679552</v>
       </c>
       <c r="P10" t="n">
-        <v>365.3910818700253</v>
+        <v>365.4727366406055</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35723,28 +35879,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.558700165376023</v>
+        <v>-0.5659755650481928</v>
       </c>
       <c r="J11" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="K11" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2291539128814352</v>
+        <v>0.2345373557794171</v>
       </c>
       <c r="M11" t="n">
-        <v>6.38354776447235</v>
+        <v>6.392344190486654</v>
       </c>
       <c r="N11" t="n">
-        <v>57.58972946218719</v>
+        <v>57.63272892375285</v>
       </c>
       <c r="O11" t="n">
-        <v>7.588789723150009</v>
+        <v>7.591622285371741</v>
       </c>
       <c r="P11" t="n">
-        <v>371.0362813404829</v>
+        <v>371.1120968753407</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35782,7 +35938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L657"/>
+  <dimension ref="A1:L660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76487,6 +76643,192 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-41.10744379971836,174.8316323824755</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-41.10753493416986,174.8325344121049</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-41.10739406120393,174.8333574307634</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-41.107003511175236,174.8340681664245</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-41.106560828253954,174.83467491994992</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-41.1060341013745,174.8351642094036</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-41.10549346580646,174.835574630265</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>-41.10489787234789,174.8359532430796</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>-41.10422714529688,174.836171488259</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>-41.103550818065926,174.83604990910345</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:08+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-41.107425679359075,174.8316283831111</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-41.10754706466689,174.83253895436053</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-41.10740922954092,174.8333684036551</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-41.10701690998106,174.83408125665056</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-41.106572576730294,174.83469201517644</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-41.106038133316105,174.83517253037326</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-41.10549693172559,174.8355877849583</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>-41.10489878075291,174.83596520782146</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>-41.104227142296374,174.836167440328</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>-41.10355190759329,174.8360352166419</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-41.10743926962855,174.83163138263419</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-41.10755598924669,174.83254229616398</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-41.10741420665124,174.83337200413632</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-41.10702089340953,174.83408514834042</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-41.106578329849164,174.83470038655247</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-41.106040173575465,174.8351767409848</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-41.105497168711466,174.83558868442458</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>-41.10489795329492,174.8359543092447</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>-41.104227128439206,174.83614874841126</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>-41.103553084983666,174.8360193393038</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L660"/>
+  <dimension ref="A1:L662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28152,6 +28152,90 @@
       <c r="L660" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>391.86</v>
+      </c>
+      <c r="C661" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="D661" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="E661" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="F661" t="n">
+        <v>369.83</v>
+      </c>
+      <c r="G661" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="H661" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="I661" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="J661" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="K661" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:06+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>392.07</v>
+      </c>
+      <c r="C662" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="D662" t="n">
+        <v>358.44</v>
+      </c>
+      <c r="E662" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="F662" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="G662" t="n">
+        <v>370.99</v>
+      </c>
+      <c r="H662" t="n">
+        <v>375.41</v>
+      </c>
+      <c r="I662" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="J662" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="K662" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28166,7 +28250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B684"/>
+  <dimension ref="A1:B686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35009,6 +35093,26 @@
       </c>
       <c r="B684" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -35177,28 +35281,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5779242330297774</v>
+        <v>0.5659151350586835</v>
       </c>
       <c r="J2" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K2" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03882547091760158</v>
+        <v>0.0374186940708694</v>
       </c>
       <c r="M2" t="n">
-        <v>15.04046904987942</v>
+        <v>15.02225223537614</v>
       </c>
       <c r="N2" t="n">
-        <v>458.1509577005945</v>
+        <v>458.019175026298</v>
       </c>
       <c r="O2" t="n">
-        <v>21.40446116351903</v>
+        <v>21.4013825494125</v>
       </c>
       <c r="P2" t="n">
-        <v>397.201028602694</v>
+        <v>397.3259120103779</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35255,28 +35359,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04821849546078461</v>
+        <v>0.0465965352407894</v>
       </c>
       <c r="J3" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K3" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01112738946215952</v>
+        <v>0.01044402415998735</v>
       </c>
       <c r="M3" t="n">
-        <v>2.623139053770883</v>
+        <v>2.623518031874555</v>
       </c>
       <c r="N3" t="n">
-        <v>11.44868578867984</v>
+        <v>11.43699664885236</v>
       </c>
       <c r="O3" t="n">
-        <v>3.383590665059803</v>
+        <v>3.381862896223376</v>
       </c>
       <c r="P3" t="n">
-        <v>369.970290380936</v>
+        <v>369.9871577014717</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35333,28 +35437,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1930865830460683</v>
+        <v>-0.195529540157782</v>
       </c>
       <c r="J4" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K4" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1307543710951681</v>
+        <v>0.1339385202913876</v>
       </c>
       <c r="M4" t="n">
-        <v>2.846586623843867</v>
+        <v>2.851069063443849</v>
       </c>
       <c r="N4" t="n">
-        <v>13.73320048267128</v>
+        <v>13.74359121569811</v>
       </c>
       <c r="O4" t="n">
-        <v>3.705833304760386</v>
+        <v>3.707234982530526</v>
       </c>
       <c r="P4" t="n">
-        <v>367.584922699655</v>
+        <v>367.6103269538268</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35411,28 +35515,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1464124092747065</v>
+        <v>-0.1484210509282186</v>
       </c>
       <c r="J5" t="n">
+        <v>661</v>
+      </c>
+      <c r="K5" t="n">
         <v>659</v>
       </c>
-      <c r="K5" t="n">
-        <v>657</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09407370386287195</v>
+        <v>0.09670866027266944</v>
       </c>
       <c r="M5" t="n">
-        <v>2.586995101698226</v>
+        <v>2.589464565337072</v>
       </c>
       <c r="N5" t="n">
-        <v>11.47027209906662</v>
+        <v>11.47073232763408</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38677901538713</v>
+        <v>3.386846959582626</v>
       </c>
       <c r="P5" t="n">
-        <v>368.3917059691648</v>
+        <v>368.4125724323478</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35489,28 +35593,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1979807226152018</v>
+        <v>-0.2021069858293933</v>
       </c>
       <c r="J6" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K6" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1715635115062797</v>
+        <v>0.1763822470954323</v>
       </c>
       <c r="M6" t="n">
-        <v>2.53241469969514</v>
+        <v>2.546816989436283</v>
       </c>
       <c r="N6" t="n">
-        <v>10.50183804215711</v>
+        <v>10.61857748462062</v>
       </c>
       <c r="O6" t="n">
-        <v>3.240653952855366</v>
+        <v>3.258615884792286</v>
       </c>
       <c r="P6" t="n">
-        <v>381.8125124265875</v>
+        <v>381.8554002143711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35567,28 +35671,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03812637608808075</v>
+        <v>-0.03940775733726867</v>
       </c>
       <c r="J7" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K7" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007752024421546988</v>
+        <v>0.008317480140875522</v>
       </c>
       <c r="M7" t="n">
-        <v>2.336150187585824</v>
+        <v>2.336232510286139</v>
       </c>
       <c r="N7" t="n">
-        <v>10.32384220993114</v>
+        <v>10.30806594163354</v>
       </c>
       <c r="O7" t="n">
-        <v>3.213073639045818</v>
+        <v>3.210617688488236</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5549256826286</v>
+        <v>373.5682422693704</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35645,28 +35749,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2010310869931074</v>
+        <v>-0.203616886858465</v>
       </c>
       <c r="J8" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K8" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L8" t="n">
-        <v>0.133689175670525</v>
+        <v>0.1369587190790442</v>
       </c>
       <c r="M8" t="n">
-        <v>2.805676277445377</v>
+        <v>2.809556929573674</v>
       </c>
       <c r="N8" t="n">
-        <v>14.43662850642227</v>
+        <v>14.45062177308179</v>
       </c>
       <c r="O8" t="n">
-        <v>3.799556356526677</v>
+        <v>3.801397344803854</v>
       </c>
       <c r="P8" t="n">
-        <v>385.0448009397102</v>
+        <v>385.0717904734617</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35723,28 +35827,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2950241905388595</v>
+        <v>-0.2991978406644959</v>
       </c>
       <c r="J9" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K9" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1497794055719412</v>
+        <v>0.1534783412797663</v>
       </c>
       <c r="M9" t="n">
-        <v>4.060036251722478</v>
+        <v>4.066041978801515</v>
       </c>
       <c r="N9" t="n">
-        <v>27.23683353124331</v>
+        <v>27.3102044313827</v>
       </c>
       <c r="O9" t="n">
-        <v>5.218891983097879</v>
+        <v>5.225916611598649</v>
       </c>
       <c r="P9" t="n">
-        <v>368.6594571208331</v>
+        <v>368.7030165963973</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35801,28 +35905,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4984854037691365</v>
+        <v>-0.5021536619294261</v>
       </c>
       <c r="J10" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K10" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L10" t="n">
-        <v>0.193400026388085</v>
+        <v>0.1963753618839521</v>
       </c>
       <c r="M10" t="n">
-        <v>6.356371096363273</v>
+        <v>6.354871971634705</v>
       </c>
       <c r="N10" t="n">
-        <v>57.13055073036779</v>
+        <v>57.07640054580382</v>
       </c>
       <c r="O10" t="n">
-        <v>7.558475423679552</v>
+        <v>7.554892490684684</v>
       </c>
       <c r="P10" t="n">
-        <v>365.4727366406055</v>
+        <v>365.5110220577668</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35879,28 +35983,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5659755650481928</v>
+        <v>-0.5685509696824709</v>
       </c>
       <c r="J11" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K11" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2345373557794171</v>
+        <v>0.2371052197161294</v>
       </c>
       <c r="M11" t="n">
-        <v>6.392344190486654</v>
+        <v>6.386339852798287</v>
       </c>
       <c r="N11" t="n">
-        <v>57.63272892375285</v>
+        <v>57.52801670096635</v>
       </c>
       <c r="O11" t="n">
-        <v>7.591622285371741</v>
+        <v>7.584722585630034</v>
       </c>
       <c r="P11" t="n">
-        <v>371.1120968753407</v>
+        <v>371.138972539686</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35938,7 +36042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L660"/>
+  <dimension ref="A1:L662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76829,6 +76933,130 @@
         </is>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-41.10745490287957,174.8316348330676</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-41.107564134008726,174.832545345966</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-41.1074202897859,174.83337640472521</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-41.10702567352346,174.83408981836888</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-41.10658250842985,174.834706466816</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-41.106042505300266,174.8351815531126</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-41.105498561003294,174.83559396878897</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>-41.10489802524784,174.83595525694702</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>-41.104227125526165,174.83614481953703</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>-41.10355337493768,174.83601542921295</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:06+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-41.10745303754848,174.83163442136808</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-41.10756682004724,174.83254635175197</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-41.10741870975094,174.83337526171502</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-41.10702755659861,174.83409165807726</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-41.1065856575049,174.83471104904407</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-41.10603643309983,174.8351690215305</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-41.10549829439422,174.83559295688937</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>-41.10489561482108,174.8359235089204</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>-41.104227108751516,174.83612219874593</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>-41.1035569510263,174.83596720475617</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L662"/>
+  <dimension ref="A1:L664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28236,6 +28236,90 @@
       <c r="L662" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:05+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="C663" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="D663" t="n">
+        <v>355.94</v>
+      </c>
+      <c r="E663" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="F663" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="G663" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="H663" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="I663" t="n">
+        <v>354.92</v>
+      </c>
+      <c r="J663" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="K663" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:07:13+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>389.03</v>
+      </c>
+      <c r="C664" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="D664" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="E664" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="F664" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="G664" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="H664" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="I664" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="J664" t="n">
+        <v>353.12</v>
+      </c>
+      <c r="K664" t="n">
+        <v>357</v>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28250,7 +28334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B686"/>
+  <dimension ref="A1:B688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35113,6 +35197,26 @@
       </c>
       <c r="B686" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -35281,28 +35385,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5659151350586835</v>
+        <v>0.5522899368287426</v>
       </c>
       <c r="J2" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K2" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0374186940708694</v>
+        <v>0.03579948568216562</v>
       </c>
       <c r="M2" t="n">
-        <v>15.02225223537614</v>
+        <v>15.0075329726757</v>
       </c>
       <c r="N2" t="n">
-        <v>458.019175026298</v>
+        <v>458.2585493609729</v>
       </c>
       <c r="O2" t="n">
-        <v>21.4013825494125</v>
+        <v>21.4069743158853</v>
       </c>
       <c r="P2" t="n">
-        <v>397.3259120103779</v>
+        <v>397.4680179496667</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35359,28 +35463,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0465965352407894</v>
+        <v>0.04312672171072137</v>
       </c>
       <c r="J3" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K3" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01044402415998735</v>
+        <v>0.008934912352211111</v>
       </c>
       <c r="M3" t="n">
-        <v>2.623518031874555</v>
+        <v>2.63323514854241</v>
       </c>
       <c r="N3" t="n">
-        <v>11.43699664885236</v>
+        <v>11.50775263584143</v>
       </c>
       <c r="O3" t="n">
-        <v>3.381862896223376</v>
+        <v>3.392307862774461</v>
       </c>
       <c r="P3" t="n">
-        <v>369.9871577014717</v>
+        <v>370.0233472981905</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35437,28 +35541,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.195529540157782</v>
+        <v>-0.1995774247907994</v>
       </c>
       <c r="J4" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K4" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1339385202913876</v>
+        <v>0.1382800899436087</v>
       </c>
       <c r="M4" t="n">
-        <v>2.851069063443849</v>
+        <v>2.864054693882364</v>
       </c>
       <c r="N4" t="n">
-        <v>13.74359121569811</v>
+        <v>13.84570414605393</v>
       </c>
       <c r="O4" t="n">
-        <v>3.707234982530526</v>
+        <v>3.720981610550357</v>
       </c>
       <c r="P4" t="n">
-        <v>367.6103269538268</v>
+        <v>367.65254624185</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35515,28 +35619,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1484210509282186</v>
+        <v>-0.1520821744129185</v>
       </c>
       <c r="J5" t="n">
+        <v>663</v>
+      </c>
+      <c r="K5" t="n">
         <v>661</v>
       </c>
-      <c r="K5" t="n">
-        <v>659</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09670866027266944</v>
+        <v>0.1006965325387935</v>
       </c>
       <c r="M5" t="n">
-        <v>2.589464565337072</v>
+        <v>2.600446327730866</v>
       </c>
       <c r="N5" t="n">
-        <v>11.47073232763408</v>
+        <v>11.55401452812979</v>
       </c>
       <c r="O5" t="n">
-        <v>3.386846959582626</v>
+        <v>3.39911966958061</v>
       </c>
       <c r="P5" t="n">
-        <v>368.4125724323478</v>
+        <v>368.4507184456122</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35593,28 +35697,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2021069858293933</v>
+        <v>-0.2078571335261124</v>
       </c>
       <c r="J6" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1763822470954323</v>
+        <v>0.1815996769807492</v>
       </c>
       <c r="M6" t="n">
-        <v>2.546816989436283</v>
+        <v>2.570144855107673</v>
       </c>
       <c r="N6" t="n">
-        <v>10.61857748462062</v>
+        <v>10.87586040787634</v>
       </c>
       <c r="O6" t="n">
-        <v>3.258615884792286</v>
+        <v>3.297856941693551</v>
       </c>
       <c r="P6" t="n">
-        <v>381.8554002143711</v>
+        <v>381.9153421746886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35671,28 +35775,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03940775733726867</v>
+        <v>-0.04124741747138071</v>
       </c>
       <c r="J7" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008317480140875522</v>
+        <v>0.009136273342561285</v>
       </c>
       <c r="M7" t="n">
-        <v>2.336232510286139</v>
+        <v>2.339404798766962</v>
       </c>
       <c r="N7" t="n">
-        <v>10.30806594163354</v>
+        <v>10.30674204837832</v>
       </c>
       <c r="O7" t="n">
-        <v>3.210617688488236</v>
+        <v>3.210411507638596</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5682422693704</v>
+        <v>373.5874202791672</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35749,28 +35853,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.203616886858465</v>
+        <v>-0.2071918085270974</v>
       </c>
       <c r="J8" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K8" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1369587190790442</v>
+        <v>0.1409698404017377</v>
       </c>
       <c r="M8" t="n">
-        <v>2.809556929573674</v>
+        <v>2.818169416189558</v>
       </c>
       <c r="N8" t="n">
-        <v>14.45062177308179</v>
+        <v>14.51784602737176</v>
       </c>
       <c r="O8" t="n">
-        <v>3.801397344803854</v>
+        <v>3.810229130560491</v>
       </c>
       <c r="P8" t="n">
-        <v>385.0717904734617</v>
+        <v>385.1092140245061</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35827,28 +35931,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2991978406644959</v>
+        <v>-0.3024242679882657</v>
       </c>
       <c r="J9" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K9" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1534783412797663</v>
+        <v>0.1566896163865119</v>
       </c>
       <c r="M9" t="n">
-        <v>4.066041978801515</v>
+        <v>4.067974621569824</v>
       </c>
       <c r="N9" t="n">
-        <v>27.3102044313827</v>
+        <v>27.31840420645393</v>
       </c>
       <c r="O9" t="n">
-        <v>5.225916611598649</v>
+        <v>5.226701082561918</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7030165963973</v>
+        <v>368.7367902463934</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35905,28 +36009,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5021536619294261</v>
+        <v>-0.5023133150419929</v>
       </c>
       <c r="J10" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K10" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1963753618839521</v>
+        <v>0.1974735300600154</v>
       </c>
       <c r="M10" t="n">
-        <v>6.354871971634705</v>
+        <v>6.339097646074913</v>
       </c>
       <c r="N10" t="n">
-        <v>57.07640054580382</v>
+        <v>56.90817739130785</v>
       </c>
       <c r="O10" t="n">
-        <v>7.554892490684684</v>
+        <v>7.543750883433774</v>
       </c>
       <c r="P10" t="n">
-        <v>365.5110220577668</v>
+        <v>365.5126898141403</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35983,28 +36087,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5685509696824709</v>
+        <v>-0.5679986223499132</v>
       </c>
       <c r="J11" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K11" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2371052197161294</v>
+        <v>0.2379005995344367</v>
       </c>
       <c r="M11" t="n">
-        <v>6.386339852798287</v>
+        <v>6.36981826008609</v>
       </c>
       <c r="N11" t="n">
-        <v>57.52801670096635</v>
+        <v>57.35687323161841</v>
       </c>
       <c r="O11" t="n">
-        <v>7.584722585630034</v>
+        <v>7.57343206423735</v>
       </c>
       <c r="P11" t="n">
-        <v>371.138972539686</v>
+        <v>371.133190659491</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36042,7 +36146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L662"/>
+  <dimension ref="A1:L664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77057,6 +77161,130 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:05+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-41.107480928689085,174.83164057725895</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-41.107591254332604,174.8325555011636</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-41.107438460187,174.8333895493463</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-41.1070444318474,174.83410814469931</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-41.10660025225413,174.8347322859145</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-41.10604294249864,174.8351824553866</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-41.105503034109404,174.8356109462165</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>-41.10489582168641,174.83592623356438</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>-41.10422707545389,174.8360773143336</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>-41.10355982418369,174.83592845930377</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:07:13+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-41.10748004043621,174.83164038121137</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-41.1075949801278,174.8325568962873</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-41.107445017331315,174.8333942928418</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-41.107050515627456,174.83411408837628</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-41.10660279573697,174.83473598694684</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-41.10604556568874,174.83518786903085</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-41.105504189414546,174.83561533111535</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>-41.104895120142864,174.8359169934674</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>-41.104227055307874,174.8360501693837</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>-41.103559701174156,174.83593011813056</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L664"/>
+  <dimension ref="A1:L665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28318,6 +28318,48 @@
         <v>357</v>
       </c>
       <c r="L664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="C665" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="D665" t="n">
+        <v>352.52</v>
+      </c>
+      <c r="E665" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="F665" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="G665" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="H665" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="I665" t="n">
+        <v>356.66</v>
+      </c>
+      <c r="J665" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="K665" t="n">
+        <v>360.35</v>
+      </c>
+      <c r="L665" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28334,7 +28376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B688"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35217,6 +35259,16 @@
       </c>
       <c r="B688" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -35385,28 +35437,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5522899368287426</v>
+        <v>0.545250331802014</v>
       </c>
       <c r="J2" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K2" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03579948568216562</v>
+        <v>0.03497068746136578</v>
       </c>
       <c r="M2" t="n">
-        <v>15.0075329726757</v>
+        <v>15.00059954595053</v>
       </c>
       <c r="N2" t="n">
-        <v>458.2585493609729</v>
+        <v>458.4222016836489</v>
       </c>
       <c r="O2" t="n">
-        <v>21.4069743158853</v>
+        <v>21.41079638135044</v>
       </c>
       <c r="P2" t="n">
-        <v>397.4680179496667</v>
+        <v>397.5419100890261</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35463,28 +35515,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04312672171072137</v>
+        <v>0.04027672494322795</v>
       </c>
       <c r="J3" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K3" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008934912352211111</v>
+        <v>0.007733582435741737</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63323514854241</v>
+        <v>2.643637796194182</v>
       </c>
       <c r="N3" t="n">
-        <v>11.50775263584143</v>
+        <v>11.63036387643384</v>
       </c>
       <c r="O3" t="n">
-        <v>3.392307862774461</v>
+        <v>3.410331930536064</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0233472981905</v>
+        <v>370.0532626638279</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35541,28 +35593,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1995774247907994</v>
+        <v>-0.2024771122210274</v>
       </c>
       <c r="J4" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K4" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1382800899436087</v>
+        <v>0.1408817254154437</v>
       </c>
       <c r="M4" t="n">
-        <v>2.864054693882364</v>
+        <v>2.875184179884696</v>
       </c>
       <c r="N4" t="n">
-        <v>13.84570414605393</v>
+        <v>13.9697167959669</v>
       </c>
       <c r="O4" t="n">
-        <v>3.720981610550357</v>
+        <v>3.737608432670135</v>
       </c>
       <c r="P4" t="n">
-        <v>367.65254624185</v>
+        <v>367.6829831920595</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35619,28 +35671,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1520821744129185</v>
+        <v>-0.1546654895616313</v>
       </c>
       <c r="J5" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K5" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1006965325387935</v>
+        <v>0.103165145463235</v>
       </c>
       <c r="M5" t="n">
-        <v>2.600446327730866</v>
+        <v>2.609774454626829</v>
       </c>
       <c r="N5" t="n">
-        <v>11.55401452812979</v>
+        <v>11.65196637585514</v>
       </c>
       <c r="O5" t="n">
-        <v>3.39911966958061</v>
+        <v>3.413497674798554</v>
       </c>
       <c r="P5" t="n">
-        <v>368.4507184456122</v>
+        <v>368.4778073636421</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35697,28 +35749,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2078571335261124</v>
+        <v>-0.2113286847158462</v>
       </c>
       <c r="J6" t="n">
+        <v>664</v>
+      </c>
+      <c r="K6" t="n">
         <v>663</v>
       </c>
-      <c r="K6" t="n">
-        <v>662</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1815996769807492</v>
+        <v>0.1841983742332879</v>
       </c>
       <c r="M6" t="n">
-        <v>2.570144855107673</v>
+        <v>2.584882203379994</v>
       </c>
       <c r="N6" t="n">
-        <v>10.87586040787634</v>
+        <v>11.06747965776199</v>
       </c>
       <c r="O6" t="n">
-        <v>3.297856941693551</v>
+        <v>3.326782177684916</v>
       </c>
       <c r="P6" t="n">
-        <v>381.9153421746886</v>
+        <v>381.9517636935782</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35775,28 +35827,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04124741747138071</v>
+        <v>-0.04256931119348684</v>
       </c>
       <c r="J7" t="n">
+        <v>664</v>
+      </c>
+      <c r="K7" t="n">
         <v>663</v>
       </c>
-      <c r="K7" t="n">
-        <v>662</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.009136273342561285</v>
+        <v>0.009728452263311982</v>
       </c>
       <c r="M7" t="n">
-        <v>2.339404798766962</v>
+        <v>2.343172790855646</v>
       </c>
       <c r="N7" t="n">
-        <v>10.30674204837832</v>
+        <v>10.32135827475317</v>
       </c>
       <c r="O7" t="n">
-        <v>3.210411507638596</v>
+        <v>3.212687080117385</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5874202791672</v>
+        <v>373.6012888279912</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35853,28 +35905,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2071918085270974</v>
+        <v>-0.2092402189047066</v>
       </c>
       <c r="J8" t="n">
+        <v>664</v>
+      </c>
+      <c r="K8" t="n">
         <v>663</v>
       </c>
-      <c r="K8" t="n">
-        <v>662</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1409698404017377</v>
+        <v>0.1431616503888375</v>
       </c>
       <c r="M8" t="n">
-        <v>2.818169416189558</v>
+        <v>2.823693344431317</v>
       </c>
       <c r="N8" t="n">
-        <v>14.51784602737176</v>
+        <v>14.56770967414212</v>
       </c>
       <c r="O8" t="n">
-        <v>3.810229130560491</v>
+        <v>3.81676691378215</v>
       </c>
       <c r="P8" t="n">
-        <v>385.1092140245061</v>
+        <v>385.1307942701596</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35931,28 +35983,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3024242679882657</v>
+        <v>-0.3036243636958786</v>
       </c>
       <c r="J9" t="n">
+        <v>664</v>
+      </c>
+      <c r="K9" t="n">
         <v>663</v>
       </c>
-      <c r="K9" t="n">
-        <v>662</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1566896163865119</v>
+        <v>0.1580506147415824</v>
       </c>
       <c r="M9" t="n">
-        <v>4.067974621569824</v>
+        <v>4.067087878978351</v>
       </c>
       <c r="N9" t="n">
-        <v>27.31840420645393</v>
+        <v>27.30183116759661</v>
       </c>
       <c r="O9" t="n">
-        <v>5.226701082561918</v>
+        <v>5.225115421461675</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7367902463934</v>
+        <v>368.7494333966434</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36009,28 +36061,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5023133150419929</v>
+        <v>-0.5011152203964381</v>
       </c>
       <c r="J10" t="n">
+        <v>664</v>
+      </c>
+      <c r="K10" t="n">
         <v>663</v>
       </c>
-      <c r="K10" t="n">
-        <v>662</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1974735300600154</v>
+        <v>0.1971626972189088</v>
       </c>
       <c r="M10" t="n">
-        <v>6.339097646074913</v>
+        <v>6.335960943380914</v>
       </c>
       <c r="N10" t="n">
-        <v>56.90817739130785</v>
+        <v>56.84689215444757</v>
       </c>
       <c r="O10" t="n">
-        <v>7.543750883433774</v>
+        <v>7.539687802187009</v>
       </c>
       <c r="P10" t="n">
-        <v>365.5126898141403</v>
+        <v>365.5000677453158</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36087,28 +36139,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5679986223499132</v>
+        <v>-0.566724879549399</v>
       </c>
       <c r="J11" t="n">
+        <v>664</v>
+      </c>
+      <c r="K11" t="n">
         <v>663</v>
       </c>
-      <c r="K11" t="n">
-        <v>662</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2379005995344367</v>
+        <v>0.2375872639154772</v>
       </c>
       <c r="M11" t="n">
-        <v>6.36981826008609</v>
+        <v>6.36655025291594</v>
       </c>
       <c r="N11" t="n">
-        <v>57.35687323161841</v>
+        <v>57.29810918040542</v>
       </c>
       <c r="O11" t="n">
-        <v>7.57343206423735</v>
+        <v>7.569551451731167</v>
       </c>
       <c r="P11" t="n">
-        <v>371.133190659491</v>
+        <v>371.1197716284049</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36146,7 +36198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L664"/>
+  <dimension ref="A1:L665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77285,6 +77337,68 @@
         </is>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-41.107486879983334,174.83164189077777</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-41.107625826245325,174.8325684466198</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-41.107465478780256,174.83340909484</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-41.10706615963177,174.83412937212222</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-41.106613999171806,174.83475228911644</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-41.1060509092233,174.835198896826</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-41.10550635190833,174.83562353874692</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>-41.10489425670364,174.83590562104058</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>-41.10422702790606,174.83601326177603</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>-41.10356264460998,174.83589042477337</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L665"/>
+  <dimension ref="A1:L666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28360,6 +28360,48 @@
         <v>360.35</v>
       </c>
       <c r="L665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="C666" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="D666" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="E666" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="F666" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="G666" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="H666" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="I666" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="J666" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="K666" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="L666" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28376,7 +28418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35269,6 +35311,16 @@
       </c>
       <c r="B689" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -35437,28 +35489,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.545250331802014</v>
+        <v>0.5382575095534824</v>
       </c>
       <c r="J2" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03497068746136578</v>
+        <v>0.03415557061387031</v>
       </c>
       <c r="M2" t="n">
-        <v>15.00059954595053</v>
+        <v>14.9936655432085</v>
       </c>
       <c r="N2" t="n">
-        <v>458.4222016836489</v>
+        <v>458.5782717113204</v>
       </c>
       <c r="O2" t="n">
-        <v>21.41079638135044</v>
+        <v>21.41444072842717</v>
       </c>
       <c r="P2" t="n">
-        <v>397.5419100890261</v>
+        <v>397.6153913795242</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35515,28 +35567,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04027672494322795</v>
+        <v>0.03739569795913064</v>
       </c>
       <c r="J3" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007733582435741737</v>
+        <v>0.006614169309729134</v>
       </c>
       <c r="M3" t="n">
-        <v>2.643637796194182</v>
+        <v>2.654158822413116</v>
       </c>
       <c r="N3" t="n">
-        <v>11.63036387643384</v>
+        <v>11.75637914869121</v>
       </c>
       <c r="O3" t="n">
-        <v>3.410331930536064</v>
+        <v>3.42875766841158</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0532626638279</v>
+        <v>370.0835367896711</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35593,28 +35645,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2024771122210274</v>
+        <v>-0.2053466572758769</v>
       </c>
       <c r="J4" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1408817254154437</v>
+        <v>0.1434700974041484</v>
       </c>
       <c r="M4" t="n">
-        <v>2.875184179884696</v>
+        <v>2.886141566775934</v>
       </c>
       <c r="N4" t="n">
-        <v>13.9697167959669</v>
+        <v>14.09107268910932</v>
       </c>
       <c r="O4" t="n">
-        <v>3.737608432670135</v>
+        <v>3.753807758677756</v>
       </c>
       <c r="P4" t="n">
-        <v>367.6829831920595</v>
+        <v>367.7131366646173</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35671,28 +35723,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1546654895616313</v>
+        <v>-0.1571351530422192</v>
       </c>
       <c r="J5" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K5" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.103165145463235</v>
+        <v>0.1055820944149409</v>
       </c>
       <c r="M5" t="n">
-        <v>2.609774454626829</v>
+        <v>2.618632784624504</v>
       </c>
       <c r="N5" t="n">
-        <v>11.65196637585514</v>
+        <v>11.74023295714097</v>
       </c>
       <c r="O5" t="n">
-        <v>3.413497674798554</v>
+        <v>3.426402334394046</v>
       </c>
       <c r="P5" t="n">
-        <v>368.4778073636421</v>
+        <v>368.5037329597143</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35749,28 +35801,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2113286847158462</v>
+        <v>-0.2148207487784377</v>
       </c>
       <c r="J6" t="n">
+        <v>665</v>
+      </c>
+      <c r="K6" t="n">
         <v>664</v>
       </c>
-      <c r="K6" t="n">
-        <v>663</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1841983742332879</v>
+        <v>0.1867782215327953</v>
       </c>
       <c r="M6" t="n">
-        <v>2.584882203379994</v>
+        <v>2.600155232009101</v>
       </c>
       <c r="N6" t="n">
-        <v>11.06747965776199</v>
+        <v>11.26203381208859</v>
       </c>
       <c r="O6" t="n">
-        <v>3.326782177684916</v>
+        <v>3.355895381576814</v>
       </c>
       <c r="P6" t="n">
-        <v>381.9517636935782</v>
+        <v>381.9884405579758</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35827,28 +35879,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04256931119348684</v>
+        <v>-0.04400281881171132</v>
       </c>
       <c r="J7" t="n">
+        <v>665</v>
+      </c>
+      <c r="K7" t="n">
         <v>664</v>
       </c>
-      <c r="K7" t="n">
-        <v>663</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.009728452263311982</v>
+        <v>0.01038553733706371</v>
       </c>
       <c r="M7" t="n">
-        <v>2.343172790855646</v>
+        <v>2.347615006723365</v>
       </c>
       <c r="N7" t="n">
-        <v>10.32135827475317</v>
+        <v>10.34140790096622</v>
       </c>
       <c r="O7" t="n">
-        <v>3.212687080117385</v>
+        <v>3.21580594889776</v>
       </c>
       <c r="P7" t="n">
-        <v>373.6012888279912</v>
+        <v>373.6163448417367</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35905,28 +35957,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2092402189047066</v>
+        <v>-0.2113320519503511</v>
       </c>
       <c r="J8" t="n">
+        <v>665</v>
+      </c>
+      <c r="K8" t="n">
         <v>664</v>
       </c>
-      <c r="K8" t="n">
-        <v>663</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1431616503888375</v>
+        <v>0.1453820565078062</v>
       </c>
       <c r="M8" t="n">
-        <v>2.823693344431317</v>
+        <v>2.829422124480707</v>
       </c>
       <c r="N8" t="n">
-        <v>14.56770967414212</v>
+        <v>14.62086724436986</v>
       </c>
       <c r="O8" t="n">
-        <v>3.81676691378215</v>
+        <v>3.823724263642694</v>
       </c>
       <c r="P8" t="n">
-        <v>385.1307942701596</v>
+        <v>385.1528559547623</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35983,28 +36035,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3036243636958786</v>
+        <v>-0.3047741074150178</v>
       </c>
       <c r="J9" t="n">
+        <v>665</v>
+      </c>
+      <c r="K9" t="n">
         <v>664</v>
       </c>
-      <c r="K9" t="n">
-        <v>663</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1580506147415824</v>
+        <v>0.159381458420077</v>
       </c>
       <c r="M9" t="n">
-        <v>4.067087878978351</v>
+        <v>4.065983171554889</v>
       </c>
       <c r="N9" t="n">
-        <v>27.30183116759661</v>
+        <v>27.28340058344951</v>
       </c>
       <c r="O9" t="n">
-        <v>5.225115421461675</v>
+        <v>5.223351470411456</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7494333966434</v>
+        <v>368.7615592607789</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36061,28 +36113,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5011152203964381</v>
+        <v>-0.4997519880987898</v>
       </c>
       <c r="J10" t="n">
+        <v>665</v>
+      </c>
+      <c r="K10" t="n">
         <v>664</v>
       </c>
-      <c r="K10" t="n">
-        <v>663</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1971626972189088</v>
+        <v>0.1967245697509411</v>
       </c>
       <c r="M10" t="n">
-        <v>6.335960943380914</v>
+        <v>6.333702151793125</v>
       </c>
       <c r="N10" t="n">
-        <v>56.84689215444757</v>
+        <v>56.79317326726976</v>
       </c>
       <c r="O10" t="n">
-        <v>7.539687802187009</v>
+        <v>7.536124552266221</v>
       </c>
       <c r="P10" t="n">
-        <v>365.5000677453158</v>
+        <v>365.4856903068039</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36139,28 +36191,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.566724879549399</v>
+        <v>-0.5650312787545626</v>
       </c>
       <c r="J11" t="n">
+        <v>665</v>
+      </c>
+      <c r="K11" t="n">
         <v>664</v>
       </c>
-      <c r="K11" t="n">
-        <v>663</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2375872639154772</v>
+        <v>0.2369346836640763</v>
       </c>
       <c r="M11" t="n">
-        <v>6.36655025291594</v>
+        <v>6.365370752197638</v>
       </c>
       <c r="N11" t="n">
-        <v>57.29810918040542</v>
+        <v>57.26104233440526</v>
       </c>
       <c r="O11" t="n">
-        <v>7.569551451731167</v>
+        <v>7.567102638025023</v>
       </c>
       <c r="P11" t="n">
-        <v>371.1197716284049</v>
+        <v>371.1019099321015</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36198,7 +36250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L665"/>
+  <dimension ref="A1:L666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77399,6 +77451,68 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-41.107486879983334,174.83164189077777</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-41.107627385880434,174.8325690306257</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-41.10746524177506,174.83340892338822</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-41.10706384200164,174.8341271078631</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-41.106614968117405,174.83475369903408</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-41.1060529009041,174.8352030071865</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-41.10550694437227,174.8356257874132</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-41.10489413977948,174.83590408102447</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>-41.10422702277796,174.83600635648165</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>-41.10356390984387,174.8358733625529</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L666"/>
+  <dimension ref="A1:L667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28372,7 +28372,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>388.26</v>
+        <v>395.58</v>
       </c>
       <c r="C666" t="n">
         <v>361.33</v>
@@ -28402,6 +28402,48 @@
         <v>361.79</v>
       </c>
       <c r="L666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:45+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>402.66</v>
+      </c>
+      <c r="C667" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="D667" t="n">
+        <v>354.27</v>
+      </c>
+      <c r="E667" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="F667" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="G667" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="H667" t="n">
+        <v>374.28</v>
+      </c>
+      <c r="I667" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="J667" t="n">
+        <v>357.34</v>
+      </c>
+      <c r="K667" t="n">
+        <v>362.19</v>
+      </c>
+      <c r="L667" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28418,7 +28460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B690"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35321,6 +35363,16 @@
       </c>
       <c r="B690" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -35489,28 +35541,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5382575095534824</v>
+        <v>0.5376655802899464</v>
       </c>
       <c r="J2" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K2" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03415557061387031</v>
+        <v>0.03421254940240137</v>
       </c>
       <c r="M2" t="n">
-        <v>14.9936655432085</v>
+        <v>14.97242027755193</v>
       </c>
       <c r="N2" t="n">
-        <v>458.5782717113204</v>
+        <v>457.5797268050097</v>
       </c>
       <c r="O2" t="n">
-        <v>21.41444072842717</v>
+        <v>21.39111326707915</v>
       </c>
       <c r="P2" t="n">
-        <v>397.6153913795242</v>
+        <v>397.6216916427306</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35567,28 +35619,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03739569795913064</v>
+        <v>0.03489229899151718</v>
       </c>
       <c r="J3" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K3" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006614169309729134</v>
+        <v>0.005729444326776467</v>
       </c>
       <c r="M3" t="n">
-        <v>2.654158822413116</v>
+        <v>2.662738333853668</v>
       </c>
       <c r="N3" t="n">
-        <v>11.75637914869121</v>
+        <v>11.84670105029718</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42875766841158</v>
+        <v>3.441903695674413</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0835367896711</v>
+        <v>370.1099159087852</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35645,28 +35697,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2053466572758769</v>
+        <v>-0.2076958637801004</v>
       </c>
       <c r="J4" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K4" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1434700974041484</v>
+        <v>0.1458537527366468</v>
       </c>
       <c r="M4" t="n">
-        <v>2.886141566775934</v>
+        <v>2.894341743343277</v>
       </c>
       <c r="N4" t="n">
-        <v>14.09107268910932</v>
+        <v>14.16499771633147</v>
       </c>
       <c r="O4" t="n">
-        <v>3.753807758677756</v>
+        <v>3.763641549926277</v>
       </c>
       <c r="P4" t="n">
-        <v>367.7131366646173</v>
+        <v>367.7378910082119</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35723,28 +35775,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1571351530422192</v>
+        <v>-0.1592066059550219</v>
       </c>
       <c r="J5" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K5" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1055820944149409</v>
+        <v>0.1077863010180513</v>
       </c>
       <c r="M5" t="n">
-        <v>2.618632784624504</v>
+        <v>2.625439711926413</v>
       </c>
       <c r="N5" t="n">
-        <v>11.74023295714097</v>
+        <v>11.79675362208133</v>
       </c>
       <c r="O5" t="n">
-        <v>3.426402334394046</v>
+        <v>3.434640246384085</v>
       </c>
       <c r="P5" t="n">
-        <v>368.5037329597143</v>
+        <v>368.5255390579944</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35801,28 +35853,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2148207487784377</v>
+        <v>-0.2177697503433254</v>
       </c>
       <c r="J6" t="n">
+        <v>666</v>
+      </c>
+      <c r="K6" t="n">
         <v>665</v>
       </c>
-      <c r="K6" t="n">
-        <v>664</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1867782215327953</v>
+        <v>0.1894134061530769</v>
       </c>
       <c r="M6" t="n">
-        <v>2.600155232009101</v>
+        <v>2.612555202461713</v>
       </c>
       <c r="N6" t="n">
-        <v>11.26203381208859</v>
+        <v>11.39520906536676</v>
       </c>
       <c r="O6" t="n">
-        <v>3.355895381576814</v>
+        <v>3.375679052482147</v>
       </c>
       <c r="P6" t="n">
-        <v>381.9884405579758</v>
+        <v>382.0195000197336</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35879,28 +35931,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04400281881171132</v>
+        <v>-0.04510440832615408</v>
       </c>
       <c r="J7" t="n">
+        <v>666</v>
+      </c>
+      <c r="K7" t="n">
         <v>665</v>
       </c>
-      <c r="K7" t="n">
-        <v>664</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01038553733706371</v>
+        <v>0.01091947958436257</v>
       </c>
       <c r="M7" t="n">
-        <v>2.347615006723365</v>
+        <v>2.350209371111152</v>
       </c>
       <c r="N7" t="n">
-        <v>10.34140790096622</v>
+        <v>10.34680290996891</v>
       </c>
       <c r="O7" t="n">
-        <v>3.21580594889776</v>
+        <v>3.216644666413888</v>
       </c>
       <c r="P7" t="n">
-        <v>373.6163448417367</v>
+        <v>373.6279469981424</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35957,28 +36009,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2113320519503511</v>
+        <v>-0.2128828262863687</v>
       </c>
       <c r="J8" t="n">
+        <v>666</v>
+      </c>
+      <c r="K8" t="n">
         <v>665</v>
       </c>
-      <c r="K8" t="n">
-        <v>664</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1453820565078062</v>
+        <v>0.1472639677737185</v>
       </c>
       <c r="M8" t="n">
-        <v>2.829422124480707</v>
+        <v>2.832513219237921</v>
       </c>
       <c r="N8" t="n">
-        <v>14.62086724436986</v>
+        <v>14.64001019650234</v>
       </c>
       <c r="O8" t="n">
-        <v>3.823724263642694</v>
+        <v>3.826226626390854</v>
       </c>
       <c r="P8" t="n">
-        <v>385.1528559547623</v>
+        <v>385.1692565967082</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36035,28 +36087,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3047741074150178</v>
+        <v>-0.3054240046704025</v>
       </c>
       <c r="J9" t="n">
+        <v>666</v>
+      </c>
+      <c r="K9" t="n">
         <v>665</v>
       </c>
-      <c r="K9" t="n">
-        <v>664</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.159381458420077</v>
+        <v>0.1603554554370059</v>
       </c>
       <c r="M9" t="n">
-        <v>4.065983171554889</v>
+        <v>4.062704613084342</v>
       </c>
       <c r="N9" t="n">
-        <v>27.28340058344951</v>
+        <v>27.24959632986203</v>
       </c>
       <c r="O9" t="n">
-        <v>5.223351470411456</v>
+        <v>5.220114589725212</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7615592607789</v>
+        <v>368.7684324285505</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36113,28 +36165,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4997519880987898</v>
+        <v>-0.4982251754272228</v>
       </c>
       <c r="J10" t="n">
+        <v>666</v>
+      </c>
+      <c r="K10" t="n">
         <v>665</v>
       </c>
-      <c r="K10" t="n">
-        <v>664</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1967245697509411</v>
+        <v>0.1961617121956006</v>
       </c>
       <c r="M10" t="n">
-        <v>6.333702151793125</v>
+        <v>6.332278019618981</v>
       </c>
       <c r="N10" t="n">
-        <v>56.79317326726976</v>
+        <v>56.74763802771191</v>
       </c>
       <c r="O10" t="n">
-        <v>7.536124552266221</v>
+        <v>7.533102815421539</v>
       </c>
       <c r="P10" t="n">
-        <v>365.4856903068039</v>
+        <v>365.4695430780527</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36191,28 +36243,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5650312787545626</v>
+        <v>-0.5632156217802987</v>
       </c>
       <c r="J11" t="n">
+        <v>666</v>
+      </c>
+      <c r="K11" t="n">
         <v>665</v>
       </c>
-      <c r="K11" t="n">
-        <v>664</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2369346836640763</v>
+        <v>0.236182315856576</v>
       </c>
       <c r="M11" t="n">
-        <v>6.365370752197638</v>
+        <v>6.364748238170235</v>
       </c>
       <c r="N11" t="n">
-        <v>57.26104233440526</v>
+        <v>57.2313149562149</v>
       </c>
       <c r="O11" t="n">
-        <v>7.567102638025023</v>
+        <v>7.565138131998311</v>
       </c>
       <c r="P11" t="n">
-        <v>371.1019099321015</v>
+        <v>371.0827079507171</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36250,7 +36302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L666"/>
+  <dimension ref="A1:L667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77459,7 +77511,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>-41.107486879983334,174.83164189077777</t>
+          <t>-41.10742185987155,174.83162754010814</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -77508,6 +77560,68 @@
         </is>
       </c>
       <c r="L666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:45+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-41.10735897156377,174.8316136599814</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-41.10761655508096,174.83256497502992</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-41.10745165347714,174.83339909348885</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-41.1070543542028,174.83411783855402</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-41.10660418859658,174.83473801370278</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-41.10604755736993,174.83519197939066</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-41.10550164181838,174.8356056618514</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-41.1048926467462,174.83588441620378</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-41.10422701800315,174.83599992741446</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>-41.103564261297294,174.83586862304708</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L667"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28372,7 +28372,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>395.58</v>
+        <v>388.26</v>
       </c>
       <c r="C666" t="n">
         <v>361.33</v>
@@ -28414,7 +28414,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>402.66</v>
+        <v>388.26</v>
       </c>
       <c r="C667" t="n">
         <v>362.58</v>
@@ -28444,6 +28444,216 @@
         <v>362.19</v>
       </c>
       <c r="L667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="C668" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="D668" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="E668" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="F668" t="n">
+        <v>367.41</v>
+      </c>
+      <c r="G668" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="H668" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="I668" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="J668" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="K668" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="C669" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="D669" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="E669" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="F669" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="G669" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="H669" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="I669" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="J669" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="K669" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="C670" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="D670" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="E670" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="F670" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="G670" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="H670" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="I670" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="J670" t="n">
+        <v>357</v>
+      </c>
+      <c r="K670" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:23+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="C671" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="D671" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="E671" t="n">
+        <v>359.02</v>
+      </c>
+      <c r="F671" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="G671" t="n">
+        <v>371.78</v>
+      </c>
+      <c r="H671" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="I671" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="J671" t="n">
+        <v>356.55</v>
+      </c>
+      <c r="K671" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="C672" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="D672" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="E672" t="n">
+        <v>359.92</v>
+      </c>
+      <c r="F672" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="G672" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="H672" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="I672" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="J672" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="K672" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="L672" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28460,7 +28670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35373,6 +35583,56 @@
       </c>
       <c r="B691" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -35541,28 +35801,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5376655802899464</v>
+        <v>0.499782748413842</v>
       </c>
       <c r="J2" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K2" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03421254940240137</v>
+        <v>0.02987153864163172</v>
       </c>
       <c r="M2" t="n">
-        <v>14.97242027755193</v>
+        <v>14.94464080275657</v>
       </c>
       <c r="N2" t="n">
-        <v>457.5797268050097</v>
+        <v>458.7842569068154</v>
       </c>
       <c r="O2" t="n">
-        <v>21.39111326707915</v>
+        <v>21.41924968122869</v>
       </c>
       <c r="P2" t="n">
-        <v>397.6216916427306</v>
+        <v>398.0213842669763</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35619,28 +35879,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03489229899151718</v>
+        <v>0.02494831436773541</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K3" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005729444326776467</v>
+        <v>0.002898450586880097</v>
       </c>
       <c r="M3" t="n">
-        <v>2.662738333853668</v>
+        <v>2.692770503517768</v>
       </c>
       <c r="N3" t="n">
-        <v>11.84670105029718</v>
+        <v>12.10961226587352</v>
       </c>
       <c r="O3" t="n">
-        <v>3.441903695674413</v>
+        <v>3.479886817968872</v>
       </c>
       <c r="P3" t="n">
-        <v>370.1099159087852</v>
+        <v>370.2148676828147</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35697,28 +35957,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2076958637801004</v>
+        <v>-0.2174894650342384</v>
       </c>
       <c r="J4" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1458537527366468</v>
+        <v>0.1566663607639908</v>
       </c>
       <c r="M4" t="n">
-        <v>2.894341743343277</v>
+        <v>2.925852065991326</v>
       </c>
       <c r="N4" t="n">
-        <v>14.16499771633147</v>
+        <v>14.40039651865231</v>
       </c>
       <c r="O4" t="n">
-        <v>3.763641549926277</v>
+        <v>3.794785437762234</v>
       </c>
       <c r="P4" t="n">
-        <v>367.7378910082119</v>
+        <v>367.8412558007824</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35775,28 +36035,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1592066059550219</v>
+        <v>-0.1671127930317619</v>
       </c>
       <c r="J5" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1077863010180513</v>
+        <v>0.1171811051448043</v>
       </c>
       <c r="M5" t="n">
-        <v>2.625439711926413</v>
+        <v>2.647670255462679</v>
       </c>
       <c r="N5" t="n">
-        <v>11.79675362208133</v>
+        <v>11.9310892861044</v>
       </c>
       <c r="O5" t="n">
-        <v>3.434640246384085</v>
+        <v>3.454140889729948</v>
       </c>
       <c r="P5" t="n">
-        <v>368.5255390579944</v>
+        <v>368.6089029025853</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35853,28 +36113,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2177697503433254</v>
+        <v>-0.2283113412471047</v>
       </c>
       <c r="J6" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K6" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1894134061530769</v>
+        <v>0.2013944073503701</v>
       </c>
       <c r="M6" t="n">
-        <v>2.612555202461713</v>
+        <v>2.651302955737592</v>
       </c>
       <c r="N6" t="n">
-        <v>11.39520906536676</v>
+        <v>11.70572387159422</v>
       </c>
       <c r="O6" t="n">
-        <v>3.375679052482147</v>
+        <v>3.421362867571083</v>
       </c>
       <c r="P6" t="n">
-        <v>382.0195000197336</v>
+        <v>382.1307058442038</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35931,28 +36191,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04510440832615408</v>
+        <v>-0.04720418536313457</v>
       </c>
       <c r="J7" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K7" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01091947958436257</v>
+        <v>0.01211257057149995</v>
       </c>
       <c r="M7" t="n">
-        <v>2.350209371111152</v>
+        <v>2.34455150487291</v>
       </c>
       <c r="N7" t="n">
-        <v>10.34680290996891</v>
+        <v>10.29178053081803</v>
       </c>
       <c r="O7" t="n">
-        <v>3.216644666413888</v>
+        <v>3.208080505663477</v>
       </c>
       <c r="P7" t="n">
-        <v>373.6279469981424</v>
+        <v>373.6500818950174</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36009,28 +36269,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2128828262863687</v>
+        <v>-0.21759310957591</v>
       </c>
       <c r="J8" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472639677737185</v>
+        <v>0.1542373490064508</v>
       </c>
       <c r="M8" t="n">
-        <v>2.832513219237921</v>
+        <v>2.833731322618459</v>
       </c>
       <c r="N8" t="n">
-        <v>14.64001019650234</v>
+        <v>14.6093356931338</v>
       </c>
       <c r="O8" t="n">
-        <v>3.826226626390854</v>
+        <v>3.82221607096378</v>
       </c>
       <c r="P8" t="n">
-        <v>385.1692565967082</v>
+        <v>385.2191507874523</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36087,28 +36347,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3054240046704025</v>
+        <v>-0.3060613190981682</v>
       </c>
       <c r="J9" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K9" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1603554554370059</v>
+        <v>0.1630864220409696</v>
       </c>
       <c r="M9" t="n">
-        <v>4.062704613084342</v>
+        <v>4.036340060312719</v>
       </c>
       <c r="N9" t="n">
-        <v>27.24959632986203</v>
+        <v>27.04960582936151</v>
       </c>
       <c r="O9" t="n">
-        <v>5.220114589725212</v>
+        <v>5.200923555423739</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7684324285505</v>
+        <v>368.775175497307</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36165,28 +36425,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4982251754272228</v>
+        <v>-0.4913807627355022</v>
       </c>
       <c r="J10" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K10" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1961617121956006</v>
+        <v>0.1938917963482447</v>
       </c>
       <c r="M10" t="n">
-        <v>6.332278019618981</v>
+        <v>6.321087735896076</v>
       </c>
       <c r="N10" t="n">
-        <v>56.74763802771191</v>
+        <v>56.48738203281878</v>
       </c>
       <c r="O10" t="n">
-        <v>7.533102815421539</v>
+        <v>7.515808807628011</v>
       </c>
       <c r="P10" t="n">
-        <v>365.4695430780527</v>
+        <v>365.3970345317783</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36243,28 +36503,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5632156217802987</v>
+        <v>-0.5548346294319205</v>
       </c>
       <c r="J11" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K11" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="L11" t="n">
-        <v>0.236182315856576</v>
+        <v>0.2329104723923904</v>
       </c>
       <c r="M11" t="n">
-        <v>6.364748238170235</v>
+        <v>6.358108262379592</v>
       </c>
       <c r="N11" t="n">
-        <v>57.2313149562149</v>
+        <v>57.05128051451935</v>
       </c>
       <c r="O11" t="n">
-        <v>7.565138131998311</v>
+        <v>7.553229806812404</v>
       </c>
       <c r="P11" t="n">
-        <v>371.0827079507171</v>
+        <v>370.9939236307766</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36302,7 +36562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L667"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77511,7 +77771,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>-41.10742185987155,174.83162754010814</t>
+          <t>-41.107486879983334,174.83164189077777</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -77573,7 +77833,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>-41.10735897156377,174.8316136599814</t>
+          <t>-41.107486879983334,174.83164189077777</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -77622,6 +77882,316 @@
         </is>
       </c>
       <c r="L667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-41.10748279402012,174.83164098895887</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-41.10760945007638,174.83256231455982</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-41.10744786139386,174.83339635026184</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-41.10704703918175,174.8341106919893</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-41.10659716373908,174.83472779180423</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-41.106043476852186,174.83518355816594</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-41.10549734645086,174.83558935902428</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-41.10489169336175,174.83587185915002</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-41.10422701658832,174.83599802250563</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>-41.10356495541722,174.83585926252294</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-41.10748279402012,174.83164098895887</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-41.107611616236326,174.8325631256787</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-41.10745023144593,174.8333980647787</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-41.107048849830576,174.83411246094082</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-41.106591168385805,174.83471906794426</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-41.10603827904892,174.83517283113122</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-41.10549734645086,174.83558935902428</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-41.10489138755888,174.83586783141584</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-41.10422702383899,174.83600778516322</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>-41.10356385712585,174.83587407347875</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-41.10746458483606,174.83163696998463</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-41.1076040779997,174.83256030298529</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-41.10744367430178,174.83339332128241</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-41.107043997291676,174.834107720151</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-41.10658632365538,174.83471201836159</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-41.10603793900568,174.83517212936263</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-41.10549539131728,174.8355819384278</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-41.10489086589487,174.83586096057527</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-41.10422702100955,174.83600397534565</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>-41.10356385712585,174.83587407347875</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:23+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-41.107462630679706,174.83163653868021</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-41.107598705922975,174.8325582914111</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-41.10744114624614,174.8333914924648</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-41.10704175208704,174.83410552665146</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-41.106585051913555,174.83471016784634</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-41.10603259546844,174.83516110157177</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-41.10549530244757,174.83558160112796</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-41.10489113572114,174.8358645144583</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-41.1042270249884,174.83600933290165</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>-41.10356305756854,174.83588485585426</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-41.107462630679706,174.83163653868021</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-41.107590907746996,174.83255537138467</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-41.10743040200932,174.8333837199917</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-41.10703523375075,174.83409915842785</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-41.106580812773956,174.8347039994626</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-41.10603045805325,174.83515669045593</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-41.10549379166216,174.835575867031</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-41.10489037121309,174.83585444512312</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-41.104227022954795,174.83600659459526</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>-41.10356404163893,174.8358715852382</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28654,6 +28654,300 @@
         <v>361.94</v>
       </c>
       <c r="L672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="C673" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="D673" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="E673" t="n">
+        <v>360.71</v>
+      </c>
+      <c r="F673" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="G673" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="H673" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="I673" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="J673" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="K673" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>392.32</v>
+      </c>
+      <c r="C674" t="n">
+        <v>366.23</v>
+      </c>
+      <c r="D674" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="E674" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="F674" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="G674" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="H674" t="n">
+        <v>377.95</v>
+      </c>
+      <c r="I674" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="J674" t="n">
+        <v>356.19</v>
+      </c>
+      <c r="K674" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:22+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>390.84</v>
+      </c>
+      <c r="C675" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="D675" t="n">
+        <v>357.76</v>
+      </c>
+      <c r="E675" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="F675" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="G675" t="n">
+        <v>372.56</v>
+      </c>
+      <c r="H675" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="I675" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="J675" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="K675" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="C676" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="D676" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="E676" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="F676" t="n">
+        <v>371.53</v>
+      </c>
+      <c r="G676" t="n">
+        <v>372.58</v>
+      </c>
+      <c r="H676" t="n">
+        <v>376.92</v>
+      </c>
+      <c r="I676" t="n">
+        <v>359.42</v>
+      </c>
+      <c r="J676" t="n">
+        <v>354.29</v>
+      </c>
+      <c r="K676" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>400.47</v>
+      </c>
+      <c r="C677" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="D677" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="E677" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="F677" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="G677" t="n">
+        <v>373.51</v>
+      </c>
+      <c r="H677" t="n">
+        <v>378.13</v>
+      </c>
+      <c r="I677" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="J677" t="n">
+        <v>353.24</v>
+      </c>
+      <c r="K677" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>407.45</v>
+      </c>
+      <c r="C678" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="D678" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="E678" t="n">
+        <v>362.73</v>
+      </c>
+      <c r="F678" t="n">
+        <v>374.48</v>
+      </c>
+      <c r="G678" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="H678" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="I678" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="J678" t="n">
+        <v>352.85</v>
+      </c>
+      <c r="K678" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>411.31</v>
+      </c>
+      <c r="C679" t="n">
+        <v>369.32</v>
+      </c>
+      <c r="D679" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="E679" t="n">
+        <v>362.73</v>
+      </c>
+      <c r="F679" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="G679" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="H679" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="I679" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="J679" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="K679" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="L679" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28670,7 +28964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B696"/>
+  <dimension ref="A1:B703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35633,6 +35927,76 @@
       </c>
       <c r="B696" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>
@@ -35801,28 +36165,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.499782748413842</v>
+        <v>0.4741048533852404</v>
       </c>
       <c r="J2" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K2" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02987153864163172</v>
+        <v>0.02741103188158744</v>
       </c>
       <c r="M2" t="n">
-        <v>14.94464080275657</v>
+        <v>14.84818039307368</v>
       </c>
       <c r="N2" t="n">
-        <v>458.7842569068154</v>
+        <v>456.3497238985866</v>
       </c>
       <c r="O2" t="n">
-        <v>21.41924968122869</v>
+        <v>21.36234359564948</v>
       </c>
       <c r="P2" t="n">
-        <v>398.0213842669763</v>
+        <v>398.2934195618027</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35879,28 +36243,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02494831436773541</v>
+        <v>0.01736437159840021</v>
       </c>
       <c r="J3" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K3" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002898450586880097</v>
+        <v>0.001417576503035423</v>
       </c>
       <c r="M3" t="n">
-        <v>2.692770503517768</v>
+        <v>2.703565008936015</v>
       </c>
       <c r="N3" t="n">
-        <v>12.10961226587352</v>
+        <v>12.15347828373754</v>
       </c>
       <c r="O3" t="n">
-        <v>3.479886817968872</v>
+        <v>3.486183914215878</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2148676828147</v>
+        <v>370.2952315045173</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35957,28 +36321,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2174894650342384</v>
+        <v>-0.223036756522685</v>
       </c>
       <c r="J4" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K4" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1566663607639908</v>
+        <v>0.1654061359535904</v>
       </c>
       <c r="M4" t="n">
-        <v>2.925852065991326</v>
+        <v>2.925559627552778</v>
       </c>
       <c r="N4" t="n">
-        <v>14.40039651865231</v>
+        <v>14.36221712994303</v>
       </c>
       <c r="O4" t="n">
-        <v>3.794785437762234</v>
+        <v>3.789751592115641</v>
       </c>
       <c r="P4" t="n">
-        <v>367.8412558007824</v>
+        <v>367.900021024639</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36035,28 +36399,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1671127930317619</v>
+        <v>-0.1720943596312221</v>
       </c>
       <c r="J5" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K5" t="n">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1171811051448043</v>
+        <v>0.1251411398656912</v>
       </c>
       <c r="M5" t="n">
-        <v>2.647670255462679</v>
+        <v>2.646807342507369</v>
       </c>
       <c r="N5" t="n">
-        <v>11.9310892861044</v>
+        <v>11.87861025968561</v>
       </c>
       <c r="O5" t="n">
-        <v>3.454140889729948</v>
+        <v>3.446535979746274</v>
       </c>
       <c r="P5" t="n">
-        <v>368.6089029025853</v>
+        <v>368.6616440490627</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36113,28 +36477,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2283113412471047</v>
+        <v>-0.2348662129845925</v>
       </c>
       <c r="J6" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K6" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2013944073503701</v>
+        <v>0.212433706969012</v>
       </c>
       <c r="M6" t="n">
-        <v>2.651302955737592</v>
+        <v>2.660210693876893</v>
       </c>
       <c r="N6" t="n">
-        <v>11.70572387159422</v>
+        <v>11.71716027198089</v>
       </c>
       <c r="O6" t="n">
-        <v>3.421362867571083</v>
+        <v>3.423033781893029</v>
       </c>
       <c r="P6" t="n">
-        <v>382.1307058442038</v>
+        <v>382.2001269277542</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36191,28 +36555,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04720418536313457</v>
+        <v>-0.04552197108885093</v>
       </c>
       <c r="J7" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K7" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01211257057149995</v>
+        <v>0.01150893722538848</v>
       </c>
       <c r="M7" t="n">
-        <v>2.34455150487291</v>
+        <v>2.328025580269907</v>
       </c>
       <c r="N7" t="n">
-        <v>10.29178053081803</v>
+        <v>10.1975825620323</v>
       </c>
       <c r="O7" t="n">
-        <v>3.208080505663477</v>
+        <v>3.193365397512833</v>
       </c>
       <c r="P7" t="n">
-        <v>373.6500818950174</v>
+        <v>373.632243804706</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36269,28 +36633,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.21759310957591</v>
+        <v>-0.2206080987114757</v>
       </c>
       <c r="J8" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K8" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1542373490064508</v>
+        <v>0.1605500022154279</v>
       </c>
       <c r="M8" t="n">
-        <v>2.833731322618459</v>
+        <v>2.818635519893811</v>
       </c>
       <c r="N8" t="n">
-        <v>14.6093356931338</v>
+        <v>14.48752693759814</v>
       </c>
       <c r="O8" t="n">
-        <v>3.82221607096378</v>
+        <v>3.806248407237518</v>
       </c>
       <c r="P8" t="n">
-        <v>385.2191507874523</v>
+        <v>385.251213883296</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36347,28 +36711,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3060613190981682</v>
+        <v>-0.3076263021744284</v>
       </c>
       <c r="J9" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K9" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1630864220409696</v>
+        <v>0.1674744154057333</v>
       </c>
       <c r="M9" t="n">
-        <v>4.036340060312719</v>
+        <v>4.003756672249387</v>
       </c>
       <c r="N9" t="n">
-        <v>27.04960582936151</v>
+        <v>26.7832259479582</v>
       </c>
       <c r="O9" t="n">
-        <v>5.200923555423739</v>
+        <v>5.175251293218349</v>
       </c>
       <c r="P9" t="n">
-        <v>368.775175497307</v>
+        <v>368.7918445773377</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36425,28 +36789,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4913807627355022</v>
+        <v>-0.4873795145525708</v>
       </c>
       <c r="J10" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K10" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1938917963482447</v>
+        <v>0.1946017669635508</v>
       </c>
       <c r="M10" t="n">
-        <v>6.321087735896076</v>
+        <v>6.277946542378355</v>
       </c>
       <c r="N10" t="n">
-        <v>56.48738203281878</v>
+        <v>55.97128426153637</v>
       </c>
       <c r="O10" t="n">
-        <v>7.515808807628011</v>
+        <v>7.481395876541781</v>
       </c>
       <c r="P10" t="n">
-        <v>365.3970345317783</v>
+        <v>365.3545048136193</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36503,28 +36867,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5548346294319205</v>
+        <v>-0.5501982474095868</v>
       </c>
       <c r="J11" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K11" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2329104723923904</v>
+        <v>0.2335521108269596</v>
       </c>
       <c r="M11" t="n">
-        <v>6.358108262379592</v>
+        <v>6.317001549327479</v>
       </c>
       <c r="N11" t="n">
-        <v>57.05128051451935</v>
+        <v>56.55930675600087</v>
       </c>
       <c r="O11" t="n">
-        <v>7.553229806812404</v>
+        <v>7.52059218120494</v>
       </c>
       <c r="P11" t="n">
-        <v>370.9939236307766</v>
+        <v>370.9446465941289</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36562,7 +36926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78197,6 +78561,440 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-41.107462630679706,174.83163653868021</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-41.107590907746996,174.83255537138467</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-41.10743040200932,174.8333837199917</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-41.10702951209967,174.83409356854372</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-41.106576755311444,174.8346980954389</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-41.10602909787983,174.83515388338233</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-41.10549299183449,174.83557283133268</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-41.10489052411477,174.83585645899015</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-41.10422702463473,174.83600885667445</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>-41.103563505672206,174.8358788129845</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-41.10745081691625,174.8316339312496</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-41.107584929145354,174.8325531326982</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-41.10742060579289,174.83337663332725</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-41.10702364559636,174.8340878371446</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-41.106568398148816,174.83468593491477</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-41.1060259889118,174.8351474672146</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-41.10549077009051,174.83556439883776</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-41.10489025428825,174.83585290510717</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-41.104227028171294,174.83601361894642</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-41.10356339144973,174.83588035332386</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:22+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-41.10746396305903,174.8316368327514</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-41.107590041283004,174.83255504693733</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-41.107424081869745,174.83337914794984</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-41.10702878784002,174.83409286096355</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-41.106572031697944,174.8346912220988</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-41.1060288064141,174.83515328186658</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-41.105493199197234,174.83557361836557</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-41.10489136057628,174.83586747602752</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-41.10422703966377,174.83602909633035</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-41.10356154631462,174.835905235728</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-41.10742505758203,174.83162824587805</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-41.10758631548776,174.83255365181384</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-41.10742068479463,174.83337669047776</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-41.10702878784002,174.83409286096355</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-41.10657221337539,174.834691486458</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-41.10602870925886,174.83515308136134</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-41.1054938212854,174.83557597946427</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-41.104891774309536,174.83587292531493</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-41.104227044967274,174.83603623973826</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-41.1035607555408,174.83591589961503</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-41.10737842430334,174.83161795340737</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-41.10757175889224,174.83254820110056</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-41.10740401542521,174.83336463172301</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-41.10702038642773,174.83408465303438</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-41.10655901147903,174.83467227635873</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-41.10602419153948,174.83514375786788</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-41.105490236871866,174.83556237503907</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-41.10489171135014,174.83587209607552</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-41.104227054247374,174.83604874070213</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-41.103559876902054,174.835927748378</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-41.10731642424657,174.8316042693469</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-41.107563527483904,174.8325451188531</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-41.10739603624786,174.83335885952508</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-41.10701488205382,174.83407927542677</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-41.106554348423074,174.83466549114203</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-41.10602103399322,174.83513724144848</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-41.10548813362018,174.83555439227788</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-41.104891846263115,174.8358738730171</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-41.10422705769391,174.83605338391726</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>-41.10355969238777,174.8359302366182</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-41.10728213768101,174.83159670195576</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-41.107558155406814,174.83254310728148</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-41.107392876177535,174.83335657350648</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-41.10701488205382,174.83407927542677</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-41.10655331891716,174.83466399310728</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-41.10602069394975,174.83513653968026</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>-41.105487867010766,174.8355533803786</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>-41.10489260177526,174.8358838238899</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>-41.10422706688379,174.83606576582423</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>-41.10355827777643,174.83594931312572</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
